--- a/data/projects/sort/raw/분류Pilot_샘플.xlsx
+++ b/data/projects/sort/raw/분류Pilot_샘플.xlsx
@@ -1523,7 +1523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1536,12 +1536,13 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1587,40 +1588,45 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>원인분류</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>조치</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>삼성 담당자</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>업체 담당자</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SW버전</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>HW버전</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>상세설명</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>사진(파일명)</t>
         </is>
@@ -1665,36 +1671,41 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>설계</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>파라미터 보정</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>v0.9.1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Rev B</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1735,36 +1746,41 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>보정 패치</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>v0.9.1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Rev B</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1805,36 +1821,41 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>타임아웃 로직 변경</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>v0.9.1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Rev B</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1875,36 +1896,41 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>운영·조작</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>청소 SOP 반영</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>v0.9.1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Rev B</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1945,36 +1971,41 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>그리퍼 Rev C 교체</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>v0.9.2</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Rev B</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2015,36 +2046,41 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>시험환경·자재</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>필터 추가</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>v0.9.2</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Rev B</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2085,36 +2121,41 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>운영·조작</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>기준점 재티칭 SOP</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>v0.9.2</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Rev C</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2155,36 +2196,41 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Rev C 전수 적용</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>v0.9.3</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Rev C</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2225,36 +2271,41 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>설계</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>v0.9.4 속도 보정</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>정상복귀</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>이OO</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>업체 김OO</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>v0.9.3</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Rev C</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
